--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/isoDateRegex-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/isoDateRegex-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="142">
-  <si>
-    <t>Statement: isoDateRegex – pattern /^\d{4}-\d{2}-\d{2}$/ used throughout the application.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="129">
+  <si>
+    <t>Statement: isoDateRegex – Tests whether a string matches the pattern /^\d{4}-\d{2}-\d{2}$/. Returns true when the input is exactly four digits, a hyphen, two digits, a hyphen, and two digits with no additional characters. Returns false for any other format. The regex validates structure only; it does not validate calendar correctness (e.g. month 99 or day 00 pass the format check).</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: string s</t>
+    <t>Input: string s passed to isoDateRegex.test(s)</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>None</t>
+    <t>No preconditions. The regex is applied directly to the input string.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: boolean</t>
+    <t>Output: boolean — true if the string matches the YYYY-MM-DD pattern, false otherwise.</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>True if YYYY-MM-DD format matches.</t>
+    <t>Result reflects only structural conformance to /^\d{4}-\d{2}-\d{2}$/. Calendar validity is not checked.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,82 +64,70 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>Valid date 1</t>
-  </si>
-  <si>
-    <t>2024-01-01</t>
-  </si>
-  <si>
-    <t>Valid date 2</t>
-  </si>
-  <si>
-    <t>1990-12-31</t>
-  </si>
-  <si>
-    <t>Slash separator</t>
-  </si>
-  <si>
-    <t>2024/01/01</t>
-  </si>
-  <si>
-    <t>Dot separator</t>
-  </si>
-  <si>
-    <t>2024.01.01</t>
-  </si>
-  <si>
-    <t>DateTime format</t>
-  </si>
-  <si>
-    <t>2024-01-01T00:00:00</t>
+    <t>Valid YYYY-MM-DD input</t>
+  </si>
+  <si>
+    <t>"2024-01-01" → true</t>
+  </si>
+  <si>
+    <t>"1990-12-31" → true</t>
+  </si>
+  <si>
+    <t>Separator character</t>
+  </si>
+  <si>
+    <t>"2024/01/01" (slash separator) → false</t>
+  </si>
+  <si>
+    <t>"2024.01.01" (dot separator) → false</t>
+  </si>
+  <si>
+    <t>Extra content</t>
+  </si>
+  <si>
+    <t>"2024-01-01T00:00:00" (datetime with time component) → false</t>
   </si>
   <si>
     <t>No separators</t>
   </si>
   <si>
-    <t>20240101</t>
+    <t>"20240101" (compact form, no separators) → false</t>
   </si>
   <si>
     <t>Reversed format</t>
   </si>
   <si>
-    <t>01-01-2024</t>
+    <t>"01-01-2024" (DD-MM-YYYY) → false</t>
   </si>
   <si>
     <t>Empty string</t>
   </si>
   <si>
-    <t>""</t>
-  </si>
-  <si>
-    <t>Month 00</t>
-  </si>
-  <si>
-    <t>2024-00-15</t>
-  </si>
-  <si>
-    <t>Day 00</t>
-  </si>
-  <si>
-    <t>2024-01-00</t>
-  </si>
-  <si>
-    <t>Month 99</t>
-  </si>
-  <si>
-    <t>2024-99-01</t>
-  </si>
-  <si>
-    <t>Day 99</t>
-  </si>
-  <si>
-    <t>2024-01-99</t>
-  </si>
-  <si>
-    <t>All zeroes</t>
-  </si>
-  <si>
-    <t>0000-00-00</t>
+    <t>"" (empty string) → false</t>
+  </si>
+  <si>
+    <t>Out-of-range month value</t>
+  </si>
+  <si>
+    <t>"2024-00-15" (month 00 passes format check) → true</t>
+  </si>
+  <si>
+    <t>Out-of-range day value</t>
+  </si>
+  <si>
+    <t>"2024-01-00" (day 00 passes format check) → true</t>
+  </si>
+  <si>
+    <t>"2024-99-01" (month 99 passes format check) → true</t>
+  </si>
+  <si>
+    <t>"2024-01-99" (day 99 passes format check) → true</t>
+  </si>
+  <si>
+    <t>All-zero digits</t>
+  </si>
+  <si>
+    <t>"0000-00-00" (all zeroes pass format check) → true</t>
   </si>
   <si>
     <t>No TC</t>
@@ -211,6 +199,9 @@
     <t>EC-8</t>
   </si>
   <si>
+    <t>"" (empty string)</t>
+  </si>
+  <si>
     <t>EC-9</t>
   </si>
   <si>
@@ -247,79 +238,79 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>Year length</t>
-  </si>
-  <si>
-    <t>3 digits (Below Min)</t>
-  </si>
-  <si>
-    <t>4 digits (At Min)</t>
-  </si>
-  <si>
-    <t>5 digits (Above Min)</t>
-  </si>
-  <si>
-    <t>Month length</t>
-  </si>
-  <si>
-    <t>1 digit (Below)</t>
-  </si>
-  <si>
-    <t>2 digits (At)</t>
-  </si>
-  <si>
-    <t>3 digits (Above)</t>
-  </si>
-  <si>
-    <t>Day length</t>
+    <t>Year digit count</t>
+  </si>
+  <si>
+    <t>year of 3 digits ("202-01-01", min − 1): below required length → false; year of 4 digits ("2024-01-01", min): exactly the required length → true; year of 5 digits ("20240-01-01", min + 1): exceeds required length → false</t>
+  </si>
+  <si>
+    <t>Month digit count</t>
+  </si>
+  <si>
+    <t>month of 1 digit ("2024-1-01", min − 1): below required length → false; month of 2 digits ("2024-01-01", min): exactly the required length → true; month of 3 digits ("2024-011-01", min + 1): exceeds required length → false</t>
+  </si>
+  <si>
+    <t>Day digit count</t>
+  </si>
+  <si>
+    <t>day of 1 digit ("2024-01-1", min − 1): below required length → false; day of 2 digits ("2024-01-01", min): exactly the required length → true; day of 3 digits ("2024-01-011", min + 1): exceeds required length → false</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Year 3d</t>
-  </si>
-  <si>
-    <t>"202-01-01"</t>
-  </si>
-  <si>
-    <t>BVA-1 Year 4d</t>
-  </si>
-  <si>
-    <t>BVA-1 Year 5d</t>
-  </si>
-  <si>
-    <t>"20240-01-01"</t>
-  </si>
-  <si>
-    <t>BVA-2 Month 1d</t>
-  </si>
-  <si>
-    <t>"2024-1-01"</t>
-  </si>
-  <si>
-    <t>BVA-2 Month 2d</t>
-  </si>
-  <si>
-    <t>BVA-2 Month 3d</t>
-  </si>
-  <si>
-    <t>"2024-011-01"</t>
-  </si>
-  <si>
-    <t>BVA-3 Day 1d</t>
-  </si>
-  <si>
-    <t>"2024-01-1"</t>
-  </si>
-  <si>
-    <t>BVA-3 Day 2d</t>
-  </si>
-  <si>
-    <t>BVA-3 Day 3d</t>
-  </si>
-  <si>
-    <t>"2024-01-011"</t>
+    <t>BVA-1 (year=3)</t>
+  </si>
+  <si>
+    <t>"202-01-01" (3-digit year)</t>
+  </si>
+  <si>
+    <t>BVA-1 (year=4)</t>
+  </si>
+  <si>
+    <t>"2024-01-01" (4-digit year)</t>
+  </si>
+  <si>
+    <t>BVA-1 (year=5)</t>
+  </si>
+  <si>
+    <t>"20240-01-01" (5-digit year)</t>
+  </si>
+  <si>
+    <t>BVA-2 (month=1)</t>
+  </si>
+  <si>
+    <t>"2024-1-01" (1-digit month)</t>
+  </si>
+  <si>
+    <t>BVA-2 (month=2)</t>
+  </si>
+  <si>
+    <t>"2024-01-01" (2-digit month)</t>
+  </si>
+  <si>
+    <t>BVA-2 (month=3)</t>
+  </si>
+  <si>
+    <t>"2024-011-01" (3-digit month)</t>
+  </si>
+  <si>
+    <t>BVA-3 (day=1)</t>
+  </si>
+  <si>
+    <t>"2024-01-1" (1-digit day)</t>
+  </si>
+  <si>
+    <t>BVA-3 (day=2)</t>
+  </si>
+  <si>
+    <t>"2024-01-01" (2-digit day)</t>
+  </si>
+  <si>
+    <t>BVA-3 (day=3)</t>
+  </si>
+  <si>
+    <t>"2024-01-011" (3-digit day)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -328,81 +319,51 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>"2024-01-01" (ISO format)</t>
-  </si>
-  <si>
-    <t>"1990-12-31" (ISO format)</t>
-  </si>
-  <si>
-    <t>"2024/01/01" (Slashes)</t>
-  </si>
-  <si>
-    <t>"2024.01.01" (Dots)</t>
-  </si>
-  <si>
-    <t>"2024-01-01T00:00:00" (DateTime)</t>
-  </si>
-  <si>
-    <t>"20240101" (No separators)</t>
-  </si>
-  <si>
-    <t>"01-01-2024" (Reversed)</t>
-  </si>
-  <si>
-    <t>"" (Empty string)</t>
-  </si>
-  <si>
-    <t>"2024-00-15" (Month 00)</t>
-  </si>
-  <si>
-    <t>"2024-01-00" (Day 00)</t>
-  </si>
-  <si>
-    <t>"2024-99-01" (Month 99)</t>
-  </si>
-  <si>
-    <t>"2024-01-99" (Day 99)</t>
-  </si>
-  <si>
-    <t>"0000-00-00" (All zeroes)</t>
+    <t>"2024-01-01" (valid YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>"1990-12-31" (valid YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>"2024/01/01" (slash separator)</t>
+  </si>
+  <si>
+    <t>"2024.01.01" (dot separator)</t>
+  </si>
+  <si>
+    <t>"2024-01-01T00:00:00" (datetime with time)</t>
+  </si>
+  <si>
+    <t>"20240101" (no separators)</t>
+  </si>
+  <si>
+    <t>"01-01-2024" (DD-MM-YYYY, reversed)</t>
+  </si>
+  <si>
+    <t>"2024-00-15" (month 00, format-only check)</t>
+  </si>
+  <si>
+    <t>"2024-01-00" (day 00, format-only check)</t>
+  </si>
+  <si>
+    <t>"2024-99-01" (month 99, format-only check)</t>
+  </si>
+  <si>
+    <t>"2024-01-99" (day 99, format-only check)</t>
+  </si>
+  <si>
+    <t>"0000-00-00" (all zeroes, format-only check)</t>
   </si>
   <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>"202-01-01" (3-digit year)</t>
-  </si>
-  <si>
-    <t>"2024-01-01" (4-digit year)</t>
-  </si>
-  <si>
-    <t>"20240-01-01" (5-digit year)</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>"2024-1-01" (1-digit month)</t>
-  </si>
-  <si>
-    <t>"2024-01-01" (2-digit month)</t>
-  </si>
-  <si>
-    <t>"2024-011-01" (3-digit month)</t>
-  </si>
-  <si>
     <t>BVA-3</t>
   </si>
   <si>
-    <t>"2024-01-1" (1-digit day)</t>
-  </si>
-  <si>
-    <t>"2024-01-01" (2-digit day)</t>
-  </si>
-  <si>
-    <t>"2024-01-011" (3-digit day)</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -433,7 +394,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>UTILS-ISO</t>
+    <t>SCHEMA-14</t>
   </si>
   <si>
     <t>n/a</t>
@@ -999,10 +960,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -1013,13 +974,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1027,13 +988,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1041,13 +1002,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1055,13 +1016,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1069,13 +1030,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1083,13 +1044,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1097,10 +1058,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>1</v>
@@ -1111,10 +1072,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>1</v>
@@ -1125,10 +1086,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>1</v>
@@ -1139,10 +1100,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>1</v>
@@ -1153,10 +1114,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>1</v>
@@ -1182,19 +1143,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1202,16 +1163,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1219,16 +1180,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1236,16 +1197,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1253,16 +1214,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1270,16 +1231,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1287,16 +1248,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1304,16 +1265,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1321,16 +1282,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1338,16 +1299,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1355,16 +1316,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1372,16 +1333,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1389,16 +1350,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1406,16 +1367,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1426,7 +1387,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1436,13 +1397,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1450,98 +1411,32 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1564,19 +1459,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1584,16 +1479,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1601,16 +1496,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1618,16 +1513,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1635,16 +1530,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1652,16 +1547,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1669,16 +1564,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1686,16 +1581,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1703,16 +1598,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1720,16 +1615,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1753,22 +1648,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1776,19 +1671,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1796,19 +1691,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1816,19 +1711,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1836,19 +1731,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1856,19 +1751,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1876,19 +1771,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1896,19 +1791,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1916,19 +1811,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1936,19 +1831,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1956,19 +1851,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1976,19 +1871,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1996,19 +1891,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2016,19 +1911,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2039,16 +1934,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2059,16 +1954,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2079,16 +1974,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2099,16 +1994,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2119,16 +2014,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2139,16 +2034,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2159,16 +2054,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2179,16 +2074,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2199,16 +2094,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2236,16 +2131,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2253,39 +2148,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B3" s="1">
         <v>22</v>
@@ -2300,19 +2195,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/isoDateRegex-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/isoDateRegex-bbt-form.xlsx
@@ -394,7 +394,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-14</t>
+    <t>SCHEMA-16</t>
   </si>
   <si>
     <t>n/a</t>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/isoDateRegex-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/isoDateRegex-bbt-form.xlsx
@@ -394,7 +394,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-16</t>
+    <t>SCHEMA-18</t>
   </si>
   <si>
     <t>n/a</t>
